--- a/TENDERER_LOTS_1-9_1410.xlsx
+++ b/TENDERER_LOTS_1-9_1410.xlsx
@@ -746,12 +746,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Соль техническая</t>
+          <t>Спецодежда, спецобувь, СИЗ</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>0851300006226000106</t>
+          <t>32616431081</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -761,154 +761,100 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>44-ФЗ запрос котировок</t>
+          <t>223-ФЗ, не аукцион</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>ЕИС / площадка из извещения</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>МКУ «Дзержинка», Новосибирск</t>
+          <t>ФБУ (Госрезерв), 18 позиций</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>г. Новосибирск, снегоотвал ул. Профилактическая, 73</t>
+          <t>Республика Башкортостан (Уфа)</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>16.10 05:00</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>11000</v>
+          <t>19.10 08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>в ЕИС не указана</t>
+        </is>
       </c>
       <c r="M5" s="9" t="n">
-        <v>4400000</v>
+        <v>3637476</v>
       </c>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>1% / 5%</t>
+          <t>см. документацию</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" s="8" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>запрет на иностранную одежду — только РФ (ГИСП)</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t>Контракт с ценой за единицу (объём не определён); МКР; концентрат минеральный — допуск эквивалента</t>
+          <t>18 позиций: ткани, ГОСТ, логотипы, размеры; цен за ед. в извещении нет</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда, спецобувь, СИЗ</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>32616431081</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ, не аукцион</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Сбербанк-АСТ</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>ФБУ (Госрезерв), 18 позиций</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан (Уфа)</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>19.10 08:00</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>в ЕИС не указана</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>3637476</v>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>см. документацию</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>не указан</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>запрет на иностранную одежду — только РФ (ГИСП)</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>18 позиций: ткани, ГОСТ, логотипы, размеры; цен за ед. в извещении нет</t>
-        </is>
-      </c>
+      <c r="A6" s="11" t="inlineStr"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Жилет сигнальный</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr"/>
+      <c r="D6" s="11" t="inlineStr"/>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
+      <c r="I6" s="11" t="inlineStr"/>
+      <c r="J6" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="11" t="inlineStr"/>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Жилет сигнальный</t>
+          <t xml:space="preserve">   Жилет утепленный</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr"/>
@@ -919,11 +865,11 @@
       <c r="H7" s="11" t="inlineStr"/>
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="12" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L7" s="13" t="n"/>
@@ -938,7 +884,7 @@
       <c r="A8" s="11" t="inlineStr"/>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Жилет утепленный</t>
+          <t xml:space="preserve">   Костюм летний мужской противоэнцэфалитный</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr"/>
@@ -949,11 +895,11 @@
       <c r="H8" s="11" t="inlineStr"/>
       <c r="I8" s="11" t="inlineStr"/>
       <c r="J8" s="12" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L8" s="13" t="n"/>
@@ -968,7 +914,7 @@
       <c r="A9" s="11" t="inlineStr"/>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской противоэнцэфалитный</t>
+          <t xml:space="preserve">   Костюм летний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr"/>
@@ -979,11 +925,11 @@
       <c r="H9" s="11" t="inlineStr"/>
       <c r="I9" s="11" t="inlineStr"/>
       <c r="J9" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L9" s="13" t="n"/>
@@ -998,7 +944,7 @@
       <c r="A10" s="11" t="inlineStr"/>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Костюм летний женский для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr"/>
@@ -1009,11 +955,11 @@
       <c r="H10" s="11" t="inlineStr"/>
       <c r="I10" s="11" t="inlineStr"/>
       <c r="J10" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L10" s="13" t="n"/>
@@ -1028,7 +974,7 @@
       <c r="A11" s="11" t="inlineStr"/>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний женский для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Куртка зимняя мужской для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr"/>
@@ -1039,11 +985,11 @@
       <c r="H11" s="11" t="inlineStr"/>
       <c r="I11" s="11" t="inlineStr"/>
       <c r="J11" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L11" s="13" t="n"/>
@@ -1058,7 +1004,7 @@
       <c r="A12" s="11" t="inlineStr"/>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка зимняя мужской для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Полукомбинезон зимний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr"/>
@@ -1073,7 +1019,7 @@
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L12" s="13" t="n"/>
@@ -1088,7 +1034,7 @@
       <c r="A13" s="11" t="inlineStr"/>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Полукомбинезон зимний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Костюм летний мужской сигнальный флуоресцентный (ОПЗ)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr"/>
@@ -1099,11 +1045,11 @@
       <c r="H13" s="11" t="inlineStr"/>
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L13" s="13" t="n"/>
@@ -1118,7 +1064,7 @@
       <c r="A14" s="11" t="inlineStr"/>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской сигнальный флуоресцентный (ОПЗ)</t>
+          <t xml:space="preserve">   Костюм зимний мужской сигнальный флуоресцентный (ОПЗ)</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr"/>
@@ -1133,7 +1079,7 @@
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L14" s="13" t="n"/>
@@ -1148,7 +1094,7 @@
       <c r="A15" s="11" t="inlineStr"/>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм зимний мужской сигнальный флуоресцентный (ОПЗ)</t>
+          <t xml:space="preserve">   Костюм зимний женский для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr"/>
@@ -1159,11 +1105,11 @@
       <c r="H15" s="11" t="inlineStr"/>
       <c r="I15" s="11" t="inlineStr"/>
       <c r="J15" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L15" s="13" t="n"/>
@@ -1178,7 +1124,7 @@
       <c r="A16" s="11" t="inlineStr"/>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм зимний женский для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Костюм зимний мужской для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr"/>
@@ -1189,11 +1135,11 @@
       <c r="H16" s="11" t="inlineStr"/>
       <c r="I16" s="11" t="inlineStr"/>
       <c r="J16" s="12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L16" s="13" t="n"/>
@@ -1208,7 +1154,7 @@
       <c r="A17" s="11" t="inlineStr"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм зимний мужской для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Костюм летний женский для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr"/>
@@ -1219,11 +1165,11 @@
       <c r="H17" s="11" t="inlineStr"/>
       <c r="I17" s="11" t="inlineStr"/>
       <c r="J17" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L17" s="13" t="n"/>
@@ -1238,7 +1184,7 @@
       <c r="A18" s="11" t="inlineStr"/>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний женский для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Костюм летний мужской для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr"/>
@@ -1249,11 +1195,11 @@
       <c r="H18" s="11" t="inlineStr"/>
       <c r="I18" s="11" t="inlineStr"/>
       <c r="J18" s="12" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="L18" s="13" t="n"/>
@@ -1268,7 +1214,7 @@
       <c r="A19" s="11" t="inlineStr"/>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Плащ для защиты от воды</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr"/>
@@ -1279,11 +1225,11 @@
       <c r="H19" s="11" t="inlineStr"/>
       <c r="I19" s="11" t="inlineStr"/>
       <c r="J19" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L19" s="13" t="n"/>
@@ -1298,7 +1244,7 @@
       <c r="A20" s="11" t="inlineStr"/>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Плащ для защиты от воды</t>
+          <t xml:space="preserve">   Футболка красная</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr"/>
@@ -1309,11 +1255,11 @@
       <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="11" t="inlineStr"/>
       <c r="J20" s="12" t="n">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L20" s="13" t="n"/>
@@ -1328,7 +1274,7 @@
       <c r="A21" s="11" t="inlineStr"/>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Футболка красная</t>
+          <t xml:space="preserve">   Халат белый мужской</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr"/>
@@ -1339,11 +1285,11 @@
       <c r="H21" s="11" t="inlineStr"/>
       <c r="I21" s="11" t="inlineStr"/>
       <c r="J21" s="12" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L21" s="13" t="n"/>
@@ -1358,7 +1304,7 @@
       <c r="A22" s="11" t="inlineStr"/>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Халат белый мужской</t>
+          <t xml:space="preserve">   Халат белый женский</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr"/>
@@ -1369,11 +1315,11 @@
       <c r="H22" s="11" t="inlineStr"/>
       <c r="I22" s="11" t="inlineStr"/>
       <c r="J22" s="12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L22" s="13" t="n"/>
@@ -1388,7 +1334,7 @@
       <c r="A23" s="11" t="inlineStr"/>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Халат белый женский</t>
+          <t xml:space="preserve">   Халат синий мужской</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr"/>
@@ -1399,11 +1345,11 @@
       <c r="H23" s="11" t="inlineStr"/>
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="12" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="L23" s="13" t="n"/>
@@ -1415,116 +1361,116 @@
       <c r="R23" s="12" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr"/>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Халат синий мужской</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr"/>
-      <c r="D24" s="11" t="inlineStr"/>
-      <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr"/>
-      <c r="H24" s="11" t="inlineStr"/>
-      <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>шт/компл</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="12" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="A24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Спецодежда, спецобувь, СИЗ</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>32616453117</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>открыть</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ запрос предложений</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>ГУП «Салаватводоканал»</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан (Салават)</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>21.10 09:00</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="8" t="inlineStr"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>см. документацию</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>не указан</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>запрет — только РФ (ГИСП)</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>Договор по ед. расценкам: объём по заявкам; классы защиты ТР ТС 019/2011</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда, спецобувь, СИЗ</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>32616453117</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ запрос предложений</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Росэлторг</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>ГУП «Салаватводоканал»</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан (Салават)</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>21.10 09:00</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>см. документацию</t>
-        </is>
-      </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>не указан</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t>запрет — только РФ (ГИСП)</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t>Договор по ед. расценкам: объём по заявкам; классы защиты ТР ТС 019/2011</t>
-        </is>
-      </c>
+      <c r="A25" s="11" t="inlineStr"/>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Костюм женский для защиты от пониженных температур, в т.ч. Куртка и полукомбинезон</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr"/>
+      <c r="F25" s="11" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>10645</v>
+      </c>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="12" t="n"/>
+      <c r="R25" s="12" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="11" t="inlineStr"/>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм женский для защиты от пониженных температур, в т.ч. Куртка и полукомбинезон</t>
+          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr"/>
@@ -1537,11 +1483,11 @@
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L26" s="13" t="n">
-        <v>10645</v>
+        <v>4410</v>
       </c>
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="12" t="n"/>
@@ -1554,7 +1500,7 @@
       <c r="A27" s="11" t="inlineStr"/>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Полукомбинезон мужской зимний</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr"/>
@@ -1567,11 +1513,11 @@
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L27" s="13" t="n">
-        <v>4410</v>
+        <v>3723.33</v>
       </c>
       <c r="M27" s="13" t="n"/>
       <c r="N27" s="12" t="n"/>
@@ -1584,7 +1530,7 @@
       <c r="A28" s="11" t="inlineStr"/>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Полукомбинезон мужской зимний</t>
+          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr"/>
@@ -1597,11 +1543,11 @@
       <c r="J28" s="12" t="n"/>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L28" s="13" t="n">
-        <v>3723.33</v>
+        <v>7856.33</v>
       </c>
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="12" t="n"/>
@@ -1614,7 +1560,7 @@
       <c r="A29" s="11" t="inlineStr"/>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Брюки мужские от защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr"/>
@@ -1627,11 +1573,11 @@
       <c r="J29" s="12" t="n"/>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L29" s="13" t="n">
-        <v>7856.33</v>
+        <v>5011.33</v>
       </c>
       <c r="M29" s="13" t="n"/>
       <c r="N29" s="12" t="n"/>
@@ -1644,7 +1590,7 @@
       <c r="A30" s="11" t="inlineStr"/>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Брюки мужские от защиты от пониженных температур</t>
+          <t xml:space="preserve">   Куртка женская для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr"/>
@@ -1657,11 +1603,11 @@
       <c r="J30" s="12" t="n"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L30" s="13" t="n">
-        <v>5011.33</v>
+        <v>4727.67</v>
       </c>
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="12" t="n"/>
@@ -1674,7 +1620,7 @@
       <c r="A31" s="11" t="inlineStr"/>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка женская для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Брюки женские от защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr"/>
@@ -1687,11 +1633,11 @@
       <c r="J31" s="12" t="n"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L31" s="13" t="n">
-        <v>4727.67</v>
+        <v>3020</v>
       </c>
       <c r="M31" s="13" t="n"/>
       <c r="N31" s="12" t="n"/>
@@ -1704,7 +1650,7 @@
       <c r="A32" s="11" t="inlineStr"/>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Брюки женские от защиты от пониженных температур</t>
+          <t xml:space="preserve">   Костюм мужской для защиты от кислот и щелочей, пониженных температур, от воздействия статического электричества</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr"/>
@@ -1717,11 +1663,11 @@
       <c r="J32" s="12" t="n"/>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L32" s="13" t="n">
-        <v>3020</v>
+        <v>14527</v>
       </c>
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="12" t="n"/>
@@ -1734,7 +1680,7 @@
       <c r="A33" s="11" t="inlineStr"/>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм мужской для защиты от кислот и щелочей, пониженных температур, от воздействия статического электричества</t>
+          <t xml:space="preserve">   Костюм сварщика зимний комбинированный со спилком</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr"/>
@@ -1747,11 +1693,11 @@
       <c r="J33" s="12" t="n"/>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L33" s="13" t="n">
-        <v>14527</v>
+        <v>12543.67</v>
       </c>
       <c r="M33" s="13" t="n"/>
       <c r="N33" s="12" t="n"/>
@@ -1764,7 +1710,7 @@
       <c r="A34" s="11" t="inlineStr"/>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм сварщика зимний комбинированный со спилком</t>
+          <t xml:space="preserve">   Костюм сигнальный для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr"/>
@@ -1777,11 +1723,11 @@
       <c r="J34" s="12" t="n"/>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L34" s="13" t="n">
-        <v>12543.67</v>
+        <v>9907</v>
       </c>
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="12" t="n"/>
@@ -1794,7 +1740,7 @@
       <c r="A35" s="11" t="inlineStr"/>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм сигнальный для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Жилет утепленный</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr"/>
@@ -1807,11 +1753,11 @@
       <c r="J35" s="12" t="n"/>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L35" s="13" t="n">
-        <v>9907</v>
+        <v>2200</v>
       </c>
       <c r="M35" s="13" t="n"/>
       <c r="N35" s="12" t="n"/>
@@ -1821,34 +1767,88 @@
       <c r="R35" s="12" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="11" t="inlineStr"/>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Жилет утепленный</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr"/>
-      <c r="D36" s="11" t="inlineStr"/>
-      <c r="E36" s="11" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr"/>
-      <c r="G36" s="11" t="inlineStr"/>
-      <c r="H36" s="11" t="inlineStr"/>
-      <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>шт/компл</t>
-        </is>
-      </c>
-      <c r="L36" s="13" t="n">
-        <v>2200</v>
-      </c>
-      <c r="M36" s="13" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="12" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="A36" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Противогололёдный реагент</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>32616449090</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>открыть</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ запрос котировок</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>площадка из извещения (223-ФЗ)</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>ГАУК «Мосгортур», Москва</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>г. Москва</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>19.10 10:00</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>54490</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>1285964</v>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>не указано / 38 578,92 ₽ (3%)</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>не указан</t>
+        </is>
+      </c>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>ограничение — российский реагент с записью ГИСП</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>Состав ПГР, фасовка, график поставки</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="n">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Противогололёдный реагент</t>
+          <t>Соль техническая</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>32616449090</t>
+          <t>0851300006226000106</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -1871,31 +1871,31 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>223-ФЗ запрос котировок</t>
+          <t>44-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>площадка из извещения (223-ФЗ)</t>
+          <t>ЕИС / площадка из извещения</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>ГАУК «Мосгортур», Москва</t>
+          <t>МКУ «Дзержинка», Новосибирск</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>г. Москва</t>
+          <t>г. Новосибирск, снегоотвал ул. Профилактическая, 73</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>19.10 10:00</t>
+          <t>16.10 05:00</t>
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>23.6</v>
+        <v>400</v>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
@@ -1903,19 +1903,19 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>54490</v>
+        <v>11000</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>1285964</v>
+        <v>4400000</v>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>не указано / 38 578,92 ₽ (3%)</t>
+          <t>1% / 5%</t>
         </is>
       </c>
       <c r="O37" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="P37" s="8" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>ограничение — российский реагент с записью ГИСП</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>Состав ПГР, фасовка, график поставки</t>
+          <t>Контракт с ценой за единицу (объём не определён); МКР; концентрат минеральный — допуск эквивалента</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Соль техническая</t>
+          <t>Запорная арматура стальная</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>0128600006826000407</t>
+          <t>32616442935</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1955,66 +1955,68 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>44-ФЗ запрос котировок</t>
+          <t>223-ФЗ иной способ (не аукцион)</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>ЕИС / площадка из извещения</t>
+          <t>ЭТП ПАО «Т Плюс»</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>МКУ УЖКХ, Струнино</t>
+          <t>ПАО «Т Плюс», Н.Новгород</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Владимирская обл., г. Струнино</t>
+          <t>Нижегородская обл. (филиал «Нижегородский»)</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>16.10 14:00</t>
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>8950</v>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>в ЕИС не указана</t>
+        </is>
       </c>
       <c r="M38" s="9" t="n">
-        <v>1342500</v>
+        <v>1883587</v>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>1% / 5%</t>
+          <t>см. документацию</t>
         </is>
       </c>
       <c r="O38" s="8" t="inlineStr">
         <is>
+          <t>не указан</t>
+        </is>
+      </c>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="P38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ограничение для 223 (ПП 1875 / квоты) — проверить</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>Галит тип С, МКР 0,8–1 т; поставка до 02.12.2026</t>
+          <t>19 позиций ЗРА: допуск аналогов энергетических вентилей; НМЦ с НДС или без</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2026,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Запорная арматура стальная</t>
+          <t>Спецодежда, спецобувь, СИЗ</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>32616442935</t>
+          <t>4634447</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -2039,68 +2041,56 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>223-ФЗ иной способ (не аукцион)</t>
+          <t>Коммерческий запрос предложений</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>ЭТП ПАО «Т Плюс»</t>
+          <t>B2B-Center</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>ПАО «Т Плюс», Н.Новгород</t>
+          <t>ООО «Биннофарм Групп» — пул поставщиков</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Нижегородская обл. (филиал «Нижегородский»)</t>
+          <t>г. Москва и филиалы Биннофарм</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>16.10 14:00</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="K39" s="8" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="L39" s="10" t="inlineStr">
-        <is>
-          <t>в ЕИС не указана</t>
-        </is>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>1883587</v>
-      </c>
+          <t>26.10 12:00</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>см. документацию</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>ограничение для 223 (ПП 1875 / квоты) — проверить</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>19 позиций ЗРА: допуск аналогов энергетических вентилей; НМЦ с НДС или без</t>
+          <t>Отбор пула поставщиков на 2026–2027: перечень позиций и образцы</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2100,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Отводы в ППУ-изоляции</t>
+          <t>Соль техническая</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>32616450774</t>
+          <t>0128600006826000407</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -2125,68 +2115,66 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>223-ФЗ иной способ (не аукцион)</t>
+          <t>44-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>РТС (Российская электронная система торгов)</t>
+          <t>ЕИС / площадка из извещения</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>МУП «Уфимские инженерные сети»</t>
+          <t>МКУ УЖКХ, Струнино</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>г. Уфа</t>
+          <t>Владимирская обл., г. Струнино</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>20.10 12:00</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>в ЕИС не указана</t>
-        </is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>8950</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>639849</v>
+        <v>1342500</v>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>см. документацию</t>
+          <t>1% / 5%</t>
         </is>
       </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>Отводы ППУ Ду108–530: длины плеч, оболочка, проводники ОДК</t>
+          <t>Галит тип С, МКР 0,8–1 т; поставка до 02.12.2026</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2184,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Спецодежда, спецобувь, СИЗ</t>
+          <t>Отводы в ППУ-изоляции</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>4634447</t>
+          <t>32616450774</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -2211,56 +2199,68 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Коммерческий запрос предложений</t>
+          <t>223-ФЗ иной способ (не аукцион)</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>B2B-Center</t>
+          <t>РТС (Российская электронная система торгов)</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>ООО «Биннофарм Групп» — пул поставщиков</t>
+          <t>МУП «Уфимские инженерные сети»</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>г. Москва и филиалы Биннофарм</t>
+          <t>г. Уфа</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>26.10 12:00</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="9" t="n"/>
+          <t>20.10 12:00</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>в ЕИС не указана</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>639849</v>
+      </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
+          <t>см. документацию</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>не указан</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>Отбор пула поставщиков на 2026–2027: перечень позиций и образцы</t>
+          <t>Отводы ППУ Ду108–530: длины плеч, оболочка, проводники ОДК</t>
         </is>
       </c>
     </row>
@@ -2268,8 +2268,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId7"/>
